--- a/editortasks_masterdoc.xlsx
+++ b/editortasks_masterdoc.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Editor Tasks'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Editor Tasks'!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -595,33 +595,471 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="104" customHeight="1">
+    <row r="3" ht="174" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>MENU-001</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>main_menu.tscn</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Layout/UI</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Rebuild main_menu.tscn: add VideoStreamPlayer background + 5-button left panel</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>See SCENE STRUCTURE comment in main_menu.gd for the full node tree.
+1. Add a VideoStreamPlayer node (full screen, autoplay=true).
+   Set stream to your menu .ogv file.
+2. Add LeftPanel (Panel, ~360px wide, left-anchored, translucent dark).
+3. Inside LeftPanel add LogoSprite + ButtonsVBox (VBoxContainer).
+4. In ButtonsVBox add 5 buttons: NewGameButton, ContinueButton, LibraryButton, SettingsButton, ExitButton.
+5. Add SaveInfoLabel (Label, italic, small) as child of ContinueButton.
+6. Add VersionLabel at the bottom of LeftPanel.
+7. Wire all button pressed signals to main_menu.gd handlers.
+8. Move existing LanguageSelection / GridContainer nodes to stay as children.
+9. Instance PresidentialLibraryPanel.tscn and SettingsPanel.tscn as children (both hidden by default).</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Main Menu rebuild</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="230" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MENU-002</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>PresidentialLibraryPanel.tscn</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>New Scene</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Create PresidentialLibraryPanel.tscn: full-screen dark overlay with 3-tab panel</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>See SCENE STRUCTURE comment in PresidentialLibraryPanel.gd.
+1. Root: Control (full screen).
+2. Add DarkOverlay (ColorRect, full screen, rgba 0,0,0,0.88).
+3. Add LibraryContainer (Panel, ~1200x800, centered).
+4. Inside LibraryContainer:
+   - SealSprite (TextureRect, presidential seal art, top-center)
+   - TitleLabel: 'PRESIDENTIAL LIBRARY' (bold, large)
+   - TabContainer with 3 tabs named: GALLERY / RECORDS / JOURNAL
+   - CloseButton (top-right)
+5. Inside each tab Control, instance the matching tab .tscn:
+   - GALLERY → GalleryTab.tscn
+   - RECORDS → RecordsTab.tscn
+   - JOURNAL → JournalTab.tscn
+6. Wire CloseButton → _on_close_button_pressed().
+7. Assign PresidentialLibraryPanel.gd as script.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Main Menu rebuild</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="188" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>MENU-003</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>GalleryTab.tscn</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>New Scene</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Create GalleryTab.tscn: 4-column grid + lightbox overlay</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>See SCENE STRUCTURE comment in GalleryTab.gd.
+1. Root: Control.
+2. Add ScrollContainer → GalleryGrid (GridContainer, columns=4, h_separation=8, v_separation=8).
+3. Add Lightbox (Control, full screen, hidden):
+   - DarkBG (ColorRect, rgba 0,0,0,0.9)
+   - FullArtRect (TextureRect, large centered, expand_mode=fit)
+   - LightboxTitle (Label, bold, bottom center)
+   - LightboxFlavor (Label, italic, smaller)
+   - PrevButton ('&lt;', left edge), NextButton ('&gt;', right edge)
+   - CloseButton ('✕', top-right)
+4. Wire all lightbox buttons to GalleryTab.gd handlers.
+5. Assign GalleryTab.gd as script.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Main Menu rebuild</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="230" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MENU-004</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>GalleryTile.tscn</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>New Scene</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Create GalleryTile.tscn: individual gallery entry tile (locked/unlocked states)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>See SCENE STRUCTURE comment in GalleryTile.gd.
+1. Root: Control (custom_minimum_size 160x200).
+2. Add Panel (NinePatchRect or Panel).
+3. Inside Panel:
+   - ArtRect (TextureRect, expand/fill, top portion)
+   - LockedOverlay (ColorRect, full size, rgba 0,0,0,0.85):
+       + LockIcon (TextureRect, 32x32, centered)
+       + LockedTitle (Label, '???', bottom center)
+   - UnlockedTitle (Label, bottom strip, visible when unlocked)
+   - HoverHint (PanelContainer, hidden by default):
+       + HintLabel (Label, autowrap)
+4. Add Area2D or mouse_entered/exited signals to root Control.
+5. Wire mouse_entered → _on_mouse_entered(), mouse_exited → _on_mouse_exited().
+6. Wire gui_input → _on_gui_input().
+7. Assign GalleryTile.gd as script.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Main Menu rebuild</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="244" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>MENU-005</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>RecordsTab.tscn</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>New Scene</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Create RecordsTab.tscn: category sidebar + entry panel (HSplitContainer)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>See SCENE STRUCTURE comment in RecordsTab.gd.
+1. Root: Control.
+2. HSplitContainer (~25% / 75% split):
+   Left: CategoryScroll (ScrollContainer) → CategoryList (VBoxContainer)
+   Right: ScrollContainer → EntryPanel (VBoxContainer, padding 12px):
+     - EntryHeader (HBoxContainer):
+         + EntryIcon (TextureRect, 64x64)
+         + EntryMeta (VBoxContainer):
+             EntryName (Label, bold, large)
+             EntryCategory (Label, italic, smaller)
+     - Divider (HSeparator)
+     - EntryBody (RichTextLabel, bbcode=on, fit_content=true)
+     - SeeAlsoBox (HBoxContainer, hidden when empty):
+         + SeeAlsoLabel (Label, 'See also:')
+         + SeeAlsoLinks (HBoxContainer)
+3. Assign RecordsTab.gd as script.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Main Menu rebuild</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="174" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MENU-006</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>JournalTab.tscn</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>New Scene</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Create JournalTab.tscn: entry list sidebar + memo document panel</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>See SCENE STRUCTURE comment in JournalTab.gd.
+1. Root: Control.
+2. HSplitContainer (~30% / 70% split):
+   Left: EntryListScroll (ScrollContainer) → EntryList (VBoxContainer)
+   Right: MemoPanel (Panel, parchment/paper texture recommended):
+     - ClassificationLabel (Label, bold caps, red color)
+     - DateLabel (Label, italic, small)
+     - SubjectLabel (Label, bold, 'RE: ...')
+     - Divider (HSeparator)
+     - MemoBody (RichTextLabel, bbcode=on, scroll_active=true)
+3. Assign JournalTab.gd as script.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Main Menu rebuild</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="370" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>MENU-007</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>SettingsPanel.tscn</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>New Scene</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Create SettingsPanel.tscn: full-screen overlay with 6-category sidebar</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>See SCENE STRUCTURE comment in SettingsPanel.gd.
+1. Root: Control (full screen).
+2. DarkOverlay (ColorRect, full screen, rgba 0,0,0,0.85).
+3. SettingsContainer (Panel, ~900x700, centered):
+   - TitleLabel: 'SETTINGS'
+   - HSplitContainer:
+       Left (SidebarScroll → SidebarList VBoxContainer, ~200px)
+       Right (ContentScroll → ContentVBox VBoxContainer):
+           AudioSection, DisplaySection, GameplaySection,
+           AccessibilitySection, LanguageSection, DataSection
+           (all VBoxContainers, hidden by default except first)
+   - CloseButton
+   - ResetConfirmDialog (ConfirmationDialog node)
+4. Populate each Section with appropriate controls:
+   Audio: 4 HSliders (Master/Music/SFX/Ambient) with labels
+   Display: CheckButton (Fullscreen), OptionButton (Resolution), HSlider (UI Scale)
+   Gameplay: OptionButton (Autosave), CheckButton (Tooltips), OptionButton (Notif Speed)
+   Accessibility: OptionButton (Text Size), OptionButton (Colorblind), CheckButton (High Contrast)
+   Language: Existing flag-picker GridContainer
+   Data: Label (description), Button ('RESET GAME DATA', red tint)
+5. Wire all controls to SettingsPanel.gd handlers.
+6. Wire CloseButton → _on_close_button_pressed().
+7. Wire ResetConfirmDialog confirmed → _on_reset_confirmed().
+8. Wire DataSection reset button → _on_reset_data_pressed().
+9. Assign SettingsPanel.gd as script.</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Main Menu rebuild</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MENU-008</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Project Settings → AutoLoad</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Game Flow</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Register LibraryData and RecordsDatabase as AutoLoads</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Project → Project Settings → AutoLoad tab.
+2. Add LibraryData.gd with node name 'LibraryData'.
+3. Add RecordsDatabase.gd with node name 'RecordsDatabase'.
+4. Ensure LibraryData loads BEFORE RecordsDatabase in the list (LibraryData must be ready first since RecordsDatabase reads it for discovery state).
+5. The existing Settings.gd autoload should remain — LibraryData.gd syncs to it automatically.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Main Menu rebuild</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="104" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
           <t>RES-001</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Resource Bar (TOP) scene</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Layout/UI</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Add Manpower, Influence, Mandate, Happiness, and Boats labels to top resource bar</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>world.gd lines 162-164 reference labels that may not exist in the bar yet:
   $MandateLabel/Label, $HarmonyLabel/Label, $InfluenceLabel/Label, $ManpowerLabel/Label
@@ -630,44 +1068,44 @@
 Match existing nodes (FoodLabel, GoldLabel, etc.) for style.</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Tile census all-resources expansion</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>WAR-001</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>WarRoomPanel.tscn</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Node Connection</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Add CloseButton node and wire its pressed signal</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Open WarRoomPanel.tscn in the editor.
 2. Add a Button node named 'CloseButton' as a child of PanelBackground.
@@ -675,44 +1113,44 @@
 4. In the Node panel, connect its 'pressed' signal to _on_close_button_pressed() in WarRoomPanel.gd (line 814).</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Commander / Protector Arc system</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="118" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="13" ht="118" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>CMD-001</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>CommanderArcEntry.tscn</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Set checkTexture and circleTexture for objective completion indicators</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>CommanderArcEntry.gd lines 33-34 have:
   var checkTexture = null   # TODO: load your checkmark asset
@@ -723,44 +1161,44 @@
 These drive the filled/empty objective row indicators.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Commander Arc system</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="118" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="14" ht="118" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>PROT-001</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>ProtectorArcEntry.tscn</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Set checkTexture and circleTexture for prayer/devotion indicators</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>ProtectorArcEntry.gd lines 33-34 have:
   var checkTexture = null   # TODO: load your checkmark asset
@@ -771,44 +1209,44 @@
 These control the prayer completion display in the Dept. of Myth. Affairs tab.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Protector Arc system</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="118" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="15" ht="118" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>SFX-001</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>world.tscn  /  AutoLoad</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>New Scene</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Create AudioManager autoload and add AudioStreamPlayer nodes for SFX bus</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>See sound_masterdoc.xlsx for the full 129-SFX catalog.
 1. Create an AudioManager.gd singleton (autoload).
@@ -819,44 +1257,44 @@
 6. Register AudioManager in Project → AutoLoad.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Sound effects planning (sound_masterdoc)</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="160" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="16" ht="160" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>SFX-002</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>world.tscn  /  all panels</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Signal Wire</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Wire SFX calls to all HIGH-priority sound trigger points</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>See sound_masterdoc.xlsx — filter Priority = HIGH for the full list.
 Key wiring points:
@@ -870,44 +1308,44 @@
 Depends on SFX-001 (AudioManager) being in place first.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Sound effects planning (sound_masterdoc)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TIP-001</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>tile_info_panel.tscn</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Layout/UI</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Verify ManaPanelContainer has enough space to show all 13 resource mana panels</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>tile_info_panel.gd now calls buildTileOutput() for up to 13 resource types (Food, Dollars, Wood, Metal, Magic, Culture, Weapons, Science, Mandate, Happiness, Manpower, Influence, Boats).
 1. Open tile_info_panel.tscn.
@@ -916,44 +1354,44 @@
 4. Consider switching to a GridContainer (3–4 columns) or a ScrollContainer wrapper if the panel overflows.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Tile census all-resources expansion</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>WAR-002</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>WarRoomPanel.tscn</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Bug Fix</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fix tab name typo: 'DEPTARTMENT' → 'DEPARTMENT' (remove double-space too)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Open WarRoomPanel.tscn.
 2. Select the tab node currently named 'DEPTARTMENT OF MYTHOLOGICAL  AFFAIRS' (note: typo + double-space).
@@ -961,44 +1399,44 @@
 4. Update the matching string in WarRoomPanel.gd line 57 to match exactly.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Commander / Protector Arc system</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="118" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="19" ht="118" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>GOV-002</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>governor_selection.tscn</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Layout/UI</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Add 'Wizard' tab/section to GovernorSelection panel (visible when tile has wizard)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>tile_info_panel.gd has a $WizardButton that shows the tile wizard's name, but there is no full wizard info view yet.
 1. Open governor_selection.tscn.
@@ -1009,44 +1447,44 @@
 3. Wire it to the changePanel('wizard') call path in tile_info_panel.gd.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Protector agree → wizard assignment</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="104" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="20" ht="104" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>MAN-001</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>mana_panel.tscn</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Add a proper Boats icon — currently reuses the Manpower icon</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>mana_panel.gd line 47-48:
   'Boats':
@@ -1056,44 +1494,44 @@
 3. Update mana_panel.gd line 48 to reference the new asset.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Tile census all-resources expansion</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="132" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="21" ht="132" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>MIL-001</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>MilitaryPanelControl scene</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Layout/UI</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Add visual separator labels between barracks groups in the military panel</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>military_panel_control.gd line 30:
   # TODO: add visual category separator labels between groups once UI nodes exist.
@@ -1104,19 +1542,19 @@
 Add Label nodes or HSeparator+Label pairs as dividers in the ScrollContainer/GridContainer hierarchy. The code will inject them dynamically once the nodes exist. Coordinate with the dev to wire the insertion logic.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Military Panel redesign</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1127,7 +1565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1165,7 +1603,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
@@ -1193,15 +1631,15 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Layout/UI</t>
+          <t>Game Flow</t>
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1211,34 +1649,44 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>New Scene</t>
+          <t>Layout/UI</t>
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Node Connection</t>
+          <t>New Scene</t>
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="D7" s="10" t="inlineStr">
         <is>
+          <t>Node Connection</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="10" t="inlineStr">
+        <is>
           <t>Signal Wire</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E8" s="10" t="n">
         <v>1</v>
       </c>
     </row>
